--- a/ReportsAndDocuments/gantt chart.xlsx
+++ b/ReportsAndDocuments/gantt chart.xlsx
@@ -5,16 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Downloads\Dev2\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Downloads\dev3\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70833A2C-0EDF-43AF-8350-0C0D5426F528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32A3F905-9C0C-424A-B3E1-6D3E033FC913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="proposal" sheetId="1" r:id="rId1"/>
+    <sheet name="final" sheetId="3" r:id="rId2"/>
+    <sheet name="midterm" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="46">
   <si>
     <t>Activity</t>
   </si>
@@ -131,13 +132,49 @@
   </si>
   <si>
     <t>Research analysis &amp; evaluation</t>
+  </si>
+  <si>
+    <t>Milestone: Midterm Report and Implementation</t>
+  </si>
+  <si>
+    <t>Milestone: progress report 2</t>
+  </si>
+  <si>
+    <t>Milestone: progress report 3</t>
+  </si>
+  <si>
+    <t>Milestone: progress report 4</t>
+  </si>
+  <si>
+    <t>Milestone: progress report 5</t>
+  </si>
+  <si>
+    <t>Milestone: Final Report and Implementation</t>
+  </si>
+  <si>
+    <t>Milestone: progress report 1</t>
+  </si>
+  <si>
+    <t>System Design &amp; Architecture</t>
+  </si>
+  <si>
+    <t>API Development &amp; Integration</t>
+  </si>
+  <si>
+    <t>ML Model Training &amp; Evaluation</t>
+  </si>
+  <si>
+    <t>Chat Module</t>
+  </si>
+  <si>
+    <t>Image Integration and UI polish</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -155,6 +192,11 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Inherit"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos (Body)"/>
     </font>
   </fonts>
   <fills count="4">
@@ -177,7 +219,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -213,11 +255,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -239,6 +296,38 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -832,6 +921,498 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D1B10C3-28B9-4F5D-AFE0-7888FF060E07}">
+  <dimension ref="B2:O28"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="37.5703125" customWidth="1"/>
+    <col min="3" max="15" width="7.28515625" style="13" customWidth="1"/>
+    <col min="16" max="16" width="14.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:15" ht="33">
+      <c r="B2" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="M2" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="2:15" ht="16.5">
+      <c r="B3" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+    </row>
+    <row r="4" spans="2:15" ht="16.5">
+      <c r="B4" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="15"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+    </row>
+    <row r="5" spans="2:15" ht="16.5">
+      <c r="B5" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="10"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
+    </row>
+    <row r="6" spans="2:15" ht="16.5">
+      <c r="B6" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="10"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="10"/>
+    </row>
+    <row r="7" spans="2:15" ht="16.5">
+      <c r="B7" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="12"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10"/>
+    </row>
+    <row r="8" spans="2:15" ht="16.5">
+      <c r="B8" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="10"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="10"/>
+    </row>
+    <row r="9" spans="2:15" ht="16.5">
+      <c r="B9" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
+    </row>
+    <row r="10" spans="2:15" ht="30">
+      <c r="B10" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+    </row>
+    <row r="11" spans="2:15" ht="16.5">
+      <c r="B11" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="14"/>
+      <c r="L11" s="14"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="10"/>
+    </row>
+    <row r="12" spans="2:15" ht="16.5">
+      <c r="B12" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="10"/>
+    </row>
+    <row r="13" spans="2:15" ht="16.5">
+      <c r="B13" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="10"/>
+    </row>
+    <row r="14" spans="2:15" ht="16.5">
+      <c r="B14" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="14"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10"/>
+    </row>
+    <row r="15" spans="2:15" ht="16.5">
+      <c r="B15" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="14"/>
+      <c r="L15" s="14"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="12"/>
+    </row>
+    <row r="16" spans="2:15" ht="16.5">
+      <c r="B16" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="14"/>
+      <c r="L16" s="14"/>
+      <c r="M16" s="14"/>
+      <c r="N16" s="14"/>
+      <c r="O16" s="11"/>
+    </row>
+    <row r="17" spans="2:15" ht="16.5">
+      <c r="B17" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="12"/>
+      <c r="N17" s="10"/>
+      <c r="O17" s="10"/>
+    </row>
+    <row r="18" spans="2:15" ht="16.5">
+      <c r="B18" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="11"/>
+      <c r="N18" s="11"/>
+      <c r="O18" s="10"/>
+    </row>
+    <row r="19" spans="2:15" ht="16.5">
+      <c r="B19" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="11"/>
+      <c r="N19" s="11"/>
+      <c r="O19" s="10"/>
+    </row>
+    <row r="20" spans="2:15" ht="16.5">
+      <c r="B20" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="14"/>
+      <c r="L20" s="14"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="10"/>
+    </row>
+    <row r="21" spans="2:15" ht="16.5">
+      <c r="B21" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="14"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="10"/>
+    </row>
+    <row r="22" spans="2:15" ht="16.5">
+      <c r="B22" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="15"/>
+      <c r="M22" s="11"/>
+      <c r="N22" s="11"/>
+      <c r="O22" s="10"/>
+    </row>
+    <row r="23" spans="2:15" ht="16.5">
+      <c r="B23" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="15"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="11"/>
+      <c r="O23" s="11"/>
+    </row>
+    <row r="24" spans="2:15" ht="16.5">
+      <c r="B24" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="14"/>
+      <c r="N24" s="14"/>
+      <c r="O24" s="14"/>
+    </row>
+    <row r="25" spans="2:15" ht="30">
+      <c r="B25" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="14"/>
+      <c r="O25" s="14"/>
+    </row>
+    <row r="26" spans="2:15">
+      <c r="B26" s="9"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="16"/>
+      <c r="I26" s="16"/>
+      <c r="J26" s="16"/>
+      <c r="K26" s="16"/>
+      <c r="L26" s="16"/>
+      <c r="M26" s="16"/>
+      <c r="N26" s="16"/>
+      <c r="O26" s="16"/>
+    </row>
+    <row r="28" spans="2:15" ht="15.75">
+      <c r="B28" s="18"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EC8E98B-99C7-4201-8539-C87FCF93C733}">
   <dimension ref="G6:O24"/>
   <sheetFormatPr defaultRowHeight="15"/>

--- a/ReportsAndDocuments/gantt chart.xlsx
+++ b/ReportsAndDocuments/gantt chart.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\300392759\Downloads\dev3\W26_4495_S3_ManeeshaE\ReportsAndDocuments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32A3F905-9C0C-424A-B3E1-6D3E033FC913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE66093E-7A27-477D-A7CC-694D263F868C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -274,7 +274,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -300,7 +300,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
@@ -922,11 +921,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D1B10C3-28B9-4F5D-AFE0-7888FF060E07}">
-  <dimension ref="B2:O28"/>
+  <dimension ref="B2:O27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="37.5703125" customWidth="1"/>
-    <col min="3" max="15" width="7.28515625" style="13" customWidth="1"/>
+    <col min="3" max="15" width="7.28515625" style="12" customWidth="1"/>
     <col min="16" max="16" width="14.140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -934,478 +933,462 @@
       <c r="B2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="G2" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="H2" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="19" t="s">
+      <c r="I2" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="19" t="s">
+      <c r="J2" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="19" t="s">
+      <c r="K2" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="L2" s="19" t="s">
+      <c r="L2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="M2" s="19" t="s">
+      <c r="M2" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="N2" s="19" t="s">
+      <c r="N2" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="19" t="s">
+      <c r="O2" s="18" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="2:15" ht="16.5">
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="10"/>
-      <c r="O3" s="10"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
     </row>
     <row r="4" spans="2:15" ht="16.5">
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="15"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="10"/>
-      <c r="O4" s="10"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
     </row>
     <row r="5" spans="2:15" ht="16.5">
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11"/>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="11"/>
-      <c r="N5" s="10"/>
-      <c r="O5" s="10"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
     </row>
     <row r="6" spans="2:15" ht="16.5">
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="10"/>
-      <c r="O6" s="10"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="9"/>
     </row>
     <row r="7" spans="2:15" ht="16.5">
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="12"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="10"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="9"/>
     </row>
     <row r="8" spans="2:15" ht="16.5">
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="14"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="10"/>
-      <c r="O8" s="10"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
     </row>
     <row r="9" spans="2:15" ht="16.5">
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="10"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="9"/>
     </row>
     <row r="10" spans="2:15" ht="30">
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
-      <c r="O10" s="10"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="14"/>
+      <c r="L10" s="14"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="9"/>
+      <c r="O10" s="9"/>
     </row>
     <row r="11" spans="2:15" ht="16.5">
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14"/>
-      <c r="K11" s="14"/>
-      <c r="L11" s="14"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="10"/>
-      <c r="O11" s="10"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="9"/>
+      <c r="O11" s="9"/>
     </row>
     <row r="12" spans="2:15" ht="16.5">
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="14"/>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="10"/>
-      <c r="N12" s="10"/>
-      <c r="O12" s="10"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="9"/>
     </row>
     <row r="13" spans="2:15" ht="16.5">
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="14"/>
-      <c r="K13" s="15"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
-      <c r="O13" s="10"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="11"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="14"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="9"/>
     </row>
     <row r="14" spans="2:15" ht="16.5">
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="14"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="10"/>
-      <c r="O14" s="10"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+      <c r="L14" s="13"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="9"/>
+      <c r="O14" s="9"/>
     </row>
     <row r="15" spans="2:15" ht="16.5">
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="12"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="13"/>
+      <c r="L15" s="13"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="11"/>
     </row>
     <row r="16" spans="2:15" ht="16.5">
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="14"/>
-      <c r="K16" s="14"/>
-      <c r="L16" s="14"/>
-      <c r="M16" s="14"/>
-      <c r="N16" s="14"/>
-      <c r="O16" s="11"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="13"/>
+      <c r="L16" s="13"/>
+      <c r="M16" s="13"/>
+      <c r="N16" s="13"/>
+      <c r="O16" s="10"/>
     </row>
     <row r="17" spans="2:15" ht="16.5">
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="15"/>
-      <c r="J17" s="14"/>
-      <c r="K17" s="14"/>
-      <c r="L17" s="15"/>
-      <c r="M17" s="12"/>
-      <c r="N17" s="10"/>
-      <c r="O17" s="10"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="14"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="9"/>
     </row>
     <row r="18" spans="2:15" ht="16.5">
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="14"/>
-      <c r="L18" s="14"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="11"/>
-      <c r="O18" s="10"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="9"/>
     </row>
     <row r="19" spans="2:15" ht="16.5">
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="14"/>
-      <c r="L19" s="14"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="11"/>
-      <c r="O19" s="10"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+      <c r="K19" s="13"/>
+      <c r="L19" s="13"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="10"/>
+      <c r="O19" s="9"/>
     </row>
     <row r="20" spans="2:15" ht="16.5">
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="15"/>
-      <c r="J20" s="15"/>
-      <c r="K20" s="14"/>
-      <c r="L20" s="14"/>
-      <c r="M20" s="10"/>
-      <c r="N20" s="10"/>
-      <c r="O20" s="10"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="11"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+      <c r="K20" s="13"/>
+      <c r="L20" s="13"/>
+      <c r="M20" s="9"/>
+      <c r="N20" s="9"/>
+      <c r="O20" s="9"/>
     </row>
     <row r="21" spans="2:15" ht="16.5">
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="15"/>
-      <c r="J21" s="15"/>
-      <c r="K21" s="15"/>
-      <c r="L21" s="14"/>
-      <c r="M21" s="11"/>
-      <c r="N21" s="10"/>
-      <c r="O21" s="10"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="11"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="14"/>
+      <c r="L21" s="13"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="9"/>
+      <c r="O21" s="9"/>
     </row>
     <row r="22" spans="2:15" ht="16.5">
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="15"/>
-      <c r="J22" s="15"/>
-      <c r="K22" s="15"/>
-      <c r="L22" s="15"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="11"/>
-      <c r="O22" s="10"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
+      <c r="K22" s="14"/>
+      <c r="L22" s="14"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="10"/>
+      <c r="O22" s="9"/>
     </row>
     <row r="23" spans="2:15" ht="16.5">
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="15"/>
-      <c r="J23" s="15"/>
-      <c r="K23" s="15"/>
-      <c r="L23" s="15"/>
-      <c r="M23" s="11"/>
-      <c r="N23" s="11"/>
-      <c r="O23" s="11"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+      <c r="K23" s="14"/>
+      <c r="L23" s="14"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="10"/>
+      <c r="O23" s="10"/>
     </row>
     <row r="24" spans="2:15" ht="16.5">
-      <c r="B24" s="17" t="s">
+      <c r="B24" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="10"/>
-      <c r="K24" s="10"/>
-      <c r="L24" s="10"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="14"/>
-      <c r="O24" s="14"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="9"/>
+      <c r="M24" s="13"/>
+      <c r="N24" s="13"/>
+      <c r="O24" s="13"/>
     </row>
     <row r="25" spans="2:15" ht="30">
-      <c r="B25" s="17" t="s">
+      <c r="B25" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="10"/>
-      <c r="K25" s="10"/>
-      <c r="L25" s="10"/>
-      <c r="M25" s="10"/>
-      <c r="N25" s="14"/>
-      <c r="O25" s="14"/>
-    </row>
-    <row r="26" spans="2:15">
-      <c r="B26" s="9"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="16"/>
-      <c r="J26" s="16"/>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="16"/>
-      <c r="O26" s="16"/>
-    </row>
-    <row r="28" spans="2:15" ht="15.75">
-      <c r="B28" s="18"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+      <c r="M25" s="9"/>
+      <c r="N25" s="13"/>
+      <c r="O25" s="13"/>
+    </row>
+    <row r="27" spans="2:15" ht="15.75">
+      <c r="B27" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
